--- a/extra tasks.xlsx
+++ b/extra tasks.xlsx
@@ -1267,6 +1267,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{6f8a142f-f8e1-47f5-bdab-718b4b85da93}" enabled="1" method="Standard" siteId="{b287c0b1-6968-4dc8-9732-8d00f2760e89}" contentBits="0" removed="0"/>
+  <clbl:label id="{6f8a142f-f8e1-47f5-bdab-718b4b85da93}" enabled="1" method="Standard" siteId="{b287c0b1-6968-4dc8-9732-8d00f2760e89}" removed="0"/>
 </clbl:labelList>
 </file>